--- a/docs/content-templates/05_lesson_explanations_template.xlsx
+++ b/docs/content-templates/05_lesson_explanations_template.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="34">
   <si>
     <t>05 — نموذج شروحات الدرس</t>
   </si>
@@ -32,12 +32,24 @@
     <t>— الأعمدة —</t>
   </si>
   <si>
+    <t>subject_code *</t>
+  </si>
+  <si>
+    <t>ملاحظة: إلزامي — يحدد المادة التي ينتمي إليها lesson_code — مثال: phys-g10-aden</t>
+  </si>
+  <si>
     <t>lesson_code *</t>
   </si>
   <si>
     <t>مثال: phys-g10-u1-l1</t>
   </si>
   <si>
+    <t>explanation_code *</t>
+  </si>
+  <si>
+    <t>ملاحظة: هوية ثابتة للشرح — لا تغيّرها بين الدفعات — مثال: EXP-PHYS-G10-U1-L1-01</t>
+  </si>
+  <si>
     <t>title *</t>
   </si>
   <si>
@@ -86,7 +98,13 @@
     <t>يمكن إضافة أكثر من شرح لنفس lesson_code.</t>
   </si>
   <si>
+    <t>phys-g10-aden</t>
+  </si>
+  <si>
     <t>phys-g10-u1-l1</t>
+  </si>
+  <si>
+    <t>EXP-PHYS-G10-U1-L1-01</t>
   </si>
   <si>
     <t>شرح النظام الدولي للوحدات</t>
@@ -493,7 +511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -566,57 +584,73 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="B11" t="s">
         <v>17</v>
       </c>
-      <c r="B13" t="s">
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="B12" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -627,15 +661,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="19" customWidth="1"/>
-    <col min="2" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="21" customWidth="1"/>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="19" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="4" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>6</v>
       </c>
@@ -651,26 +687,38 @@
       <c r="E1" s="3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D2">
+        <v>30</v>
+      </c>
+      <c r="D2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2">
         <v>1</v>
       </c>
-      <c r="E2" t="s">
-        <v>27</v>
+      <c r="G2" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E1"/>
+  <autoFilter ref="A1:G1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
